--- a/correctionProfile/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:57:50+00:00</t>
+    <t>2026-09-17T15:33:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T15:33:46+00:00</t>
+    <t>2026-09-28T13:37:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T13:37:45+00:00</t>
+    <t>2026-09-29T08:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1140,7 +1140,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260916095455</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1226,7 +1226,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationMethod-cisis|20260716085851</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationMethod-cisis|20260916095453</t>
   </si>
   <si>
     <t>OBX-17</t>

--- a/correctionProfile/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:08:01+00:00</t>
+    <t>2026-09-29T09:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T09:01:26+00:00</t>
+    <t>2026-09-30T14:16:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
